--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED24.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED24.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>260W</t>
+          <t>275.55W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0149</t>
+          <t>SIM_XA_FIXED-2-0074</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>141W</t>
+          <t>149W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3季</t>
+          <t>0季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,14 +1748,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-4-0037</t>
+          <t>SIM_XA_FIXED-3-0037</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>121W</t>
+          <t>167W</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1783,17 +1783,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>第4年</t>
+          <t>第3年</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1803,14 +1803,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第3年4季</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-4-0043</t>
+          <t>SIM_XA_FIXED-4-0004</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1824,11 +1824,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>74W</t>
+          <t>80W</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>5季</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年3季</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G56"/>
+  <dimension ref="B2:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2244,14 +2244,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Auction_Win</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>auction_bid_fee | {"order_id": "SIM_XA_FIXED-2-0165"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2270,23 +2270,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-14</v>
+        <v>-48</v>
       </c>
       <c r="E17" t="n">
-        <v>442</v>
+        <v>404</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>第2年2季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2296,14 +2296,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-14</v>
+        <v>-32</v>
       </c>
       <c r="E18" t="n">
-        <v>428</v>
+        <v>372</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-7c9308137a", "line_id": "L-30ae9055cf", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-48</v>
+        <v>-14</v>
       </c>
       <c r="E19" t="n">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2348,14 +2348,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="E20" t="n">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-71559e992f", "line_id": "L-30ae9055cf", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2374,14 +2374,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E21" t="n">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-30ae9055cf"}</t>
         </is>
       </c>
     </row>
@@ -2400,14 +2400,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-30ae9055cf"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30ae9055cf", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30ae9055cf", "asset_type": "factory"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30ae9055cf", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2452,23 +2452,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="E24" t="n">
-        <v>319</v>
+        <v>478</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30ae9055cf", "asset_type": "production_line"}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0074", "receivable_term_quarters": 0, "revenue_wan": 149.0}</t>
         </is>
       </c>
     </row>
@@ -2478,14 +2478,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-12</v>
+        <v>-48</v>
       </c>
       <c r="E25" t="n">
-        <v>307</v>
+        <v>430</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2504,14 +2504,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-14</v>
+        <v>-32</v>
       </c>
       <c r="E26" t="n">
-        <v>293</v>
+        <v>398</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-0f1d65c14e", "line_id": "L-30ae9055cf", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2530,23 +2530,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E27" t="n">
-        <v>293</v>
+        <v>386</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0149", "receivable_term_quarters": 3, "revenue_wan": 141.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2556,23 +2556,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-48</v>
+        <v>-14</v>
       </c>
       <c r="E28" t="n">
-        <v>245</v>
+        <v>372</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2582,14 +2582,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="E29" t="n">
-        <v>213</v>
+        <v>358</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-db27dcb649", "line_id": "L-30ae9055cf", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2615,11 +2615,11 @@
         <v>-14</v>
       </c>
       <c r="E30" t="n">
-        <v>199</v>
+        <v>344</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2634,23 +2634,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>344</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-3-0037", "receivable_term_quarters": 4, "revenue_wan": 167.0}</t>
         </is>
       </c>
     </row>
@@ -2660,14 +2660,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-14</v>
+        <v>-48</v>
       </c>
       <c r="E32" t="n">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>141</v>
+        <v>-32</v>
       </c>
       <c r="E33" t="n">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-c167503cf3"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-cb123562c8", "line_id": "L-30ae9055cf", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2712,14 +2712,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E34" t="n">
-        <v>297</v>
+        <v>250</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-30ae9055cf"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2738,14 +2738,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E35" t="n">
-        <v>297</v>
+        <v>235</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30ae9055cf", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-30ae9055cf"}</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>297</v>
+        <v>235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30ae9055cf", "asset_type": "production_line"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30ae9055cf", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2790,23 +2790,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>285</v>
+        <v>235</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30ae9055cf", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2816,23 +2816,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>income_tax_expense</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-14</v>
+        <v>-14.45</v>
       </c>
       <c r="E38" t="n">
-        <v>271</v>
+        <v>220.55</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>income_tax_expense | {"pretax_income_wan": 57.8}</t>
         </is>
       </c>
     </row>
@@ -2842,23 +2842,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E39" t="n">
-        <v>271</v>
+        <v>208.55</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-4-0037", "receivable_term_quarters": 1, "revenue_wan": 121.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2868,23 +2868,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-48</v>
+        <v>-14</v>
       </c>
       <c r="E40" t="n">
-        <v>223</v>
+        <v>194.55</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2894,14 +2894,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="E41" t="n">
-        <v>191</v>
+        <v>180.55</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-4251583979", "line_id": "L-30ae9055cf", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2920,23 +2920,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-14</v>
+        <v>80</v>
       </c>
       <c r="E42" t="n">
-        <v>177</v>
+        <v>260.55</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-4-0004", "receivable_term_quarters": 0, "revenue_wan": 80.0}</t>
         </is>
       </c>
     </row>
@@ -2946,23 +2946,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>121</v>
+        <v>-24</v>
       </c>
       <c r="E43" t="n">
-        <v>298</v>
+        <v>236.55</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-ee8f0626bd"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2972,14 +2972,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="E44" t="n">
-        <v>284</v>
+        <v>220.55</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-83dc613311", "line_id": "L-30ae9055cf", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -3005,11 +3005,11 @@
         <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>270</v>
+        <v>206.55</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3024,23 +3024,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-15</v>
+        <v>167</v>
       </c>
       <c r="E46" t="n">
-        <v>255</v>
+        <v>373.55</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-30ae9055cf"}</t>
+          <t>receivable_collected | {"receivable_id": "AR-c8f5451a0e"}</t>
         </is>
       </c>
     </row>
@@ -3050,14 +3050,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E47" t="n">
-        <v>255</v>
+        <v>359.55</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30ae9055cf", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3076,14 +3076,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E48" t="n">
-        <v>255</v>
+        <v>344.55</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30ae9055cf", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-30ae9055cf"}</t>
         </is>
       </c>
     </row>
@@ -3102,23 +3102,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>329</v>
+        <v>344.55</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-4-0043", "receivable_term_quarters": 0, "revenue_wan": 74.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30ae9055cf", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3128,23 +3128,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>317</v>
+        <v>344.55</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30ae9055cf", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -3154,14 +3154,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E51" t="n">
-        <v>303</v>
+        <v>332.55</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -3187,11 +3187,11 @@
         <v>-14</v>
       </c>
       <c r="E52" t="n">
-        <v>289</v>
+        <v>318.55</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3213,11 +3213,11 @@
         <v>-14</v>
       </c>
       <c r="E53" t="n">
-        <v>275</v>
+        <v>304.55</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3232,23 +3232,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E54" t="n">
-        <v>260</v>
+        <v>290.55</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-30ae9055cf"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3258,14 +3258,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E55" t="n">
-        <v>260</v>
+        <v>275.55</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30ae9055cf", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-30ae9055cf"}</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>260</v>
+        <v>275.55</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3299,6 +3299,32 @@
         </is>
       </c>
       <c r="G56" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30ae9055cf", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>54</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30ae9055cf", "asset_type": "production_line"}</t>
         </is>
@@ -3695,13 +3721,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>141</v>
+        <v>316</v>
       </c>
       <c r="G16" t="n">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="H16" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3720,13 +3746,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G17" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3745,13 +3771,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="G18" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="H18" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3795,13 +3821,13 @@
         <v>-83</v>
       </c>
       <c r="F20" t="n">
-        <v>-22</v>
+        <v>73</v>
       </c>
       <c r="G20" t="n">
-        <v>-42</v>
+        <v>-63</v>
       </c>
       <c r="H20" t="n">
-        <v>-35</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3871,13 @@
         <v>-98.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-37.2</v>
+        <v>57.8</v>
       </c>
       <c r="G22" t="n">
-        <v>-57.2</v>
+        <v>-78.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-50.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="23">
@@ -3892,16 +3918,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-108.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-37.2</v>
+        <v>57.8</v>
       </c>
       <c r="G24" t="n">
-        <v>-57.2</v>
+        <v>-78.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-50.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="25">
@@ -3920,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>14.45</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -3942,16 +3968,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-108.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-37.2</v>
+        <v>43.35</v>
       </c>
       <c r="G26" t="n">
-        <v>-57.2</v>
+        <v>-78.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-50.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="28">
@@ -4041,16 +4067,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="F30" t="n">
-        <v>297</v>
+        <v>220.55</v>
       </c>
       <c r="G30" t="n">
-        <v>255</v>
+        <v>344.55</v>
       </c>
       <c r="H30" t="n">
-        <v>260</v>
+        <v>275.55</v>
       </c>
     </row>
     <row r="31">
@@ -4069,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -4091,10 +4117,10 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
         <v>80</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -4116,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F33" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H33" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
@@ -4166,16 +4192,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F35" t="n">
-        <v>377</v>
+        <v>467.55</v>
       </c>
       <c r="G35" t="n">
-        <v>335</v>
+        <v>404.55</v>
       </c>
       <c r="H35" t="n">
-        <v>300</v>
+        <v>335.55</v>
       </c>
     </row>
     <row r="36">
@@ -4291,16 +4317,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>480.6</v>
+        <v>490.6</v>
       </c>
       <c r="F40" t="n">
-        <v>443.4</v>
+        <v>533.95</v>
       </c>
       <c r="G40" t="n">
-        <v>386.2</v>
+        <v>455.75</v>
       </c>
       <c r="H40" t="n">
-        <v>336</v>
+        <v>371.55</v>
       </c>
     </row>
     <row r="41">
@@ -4469,13 +4495,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-194.4000000000001</v>
+        <v>-184.4000000000002</v>
       </c>
       <c r="G47" t="n">
-        <v>-231.6000000000001</v>
+        <v>-141.0500000000002</v>
       </c>
       <c r="H47" t="n">
-        <v>-288.8000000000001</v>
+        <v>-219.2500000000002</v>
       </c>
     </row>
     <row r="48">
@@ -4491,16 +4517,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-108.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-37.2</v>
+        <v>43.35</v>
       </c>
       <c r="G48" t="n">
-        <v>-57.2</v>
+        <v>-78.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-50.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="49">
@@ -4516,16 +4542,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>480.6</v>
+        <v>490.6</v>
       </c>
       <c r="F49" t="n">
-        <v>443.3999999999999</v>
+        <v>533.9499999999998</v>
       </c>
       <c r="G49" t="n">
-        <v>386.1999999999999</v>
+        <v>455.7499999999998</v>
       </c>
       <c r="H49" t="n">
-        <v>335.9999999999999</v>
+        <v>371.5499999999998</v>
       </c>
     </row>
     <row r="50">
@@ -4541,16 +4567,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>480.6</v>
+        <v>490.6</v>
       </c>
       <c r="F50" t="n">
-        <v>443.3999999999999</v>
+        <v>533.9499999999998</v>
       </c>
       <c r="G50" t="n">
-        <v>386.1999999999999</v>
+        <v>455.7499999999998</v>
       </c>
       <c r="H50" t="n">
-        <v>335.9999999999999</v>
+        <v>371.5499999999998</v>
       </c>
     </row>
   </sheetData>
